--- a/android/app/src/test/resources/wechat_bill_test.xlsx
+++ b/android/app/src/test/resources/wechat_bill_test.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>702875366606343249856721400021449540</t>
+          <t>145524795938735547867909404750439930</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2104259460313224851655266767005</t>
+          <t>8115172330892815761231121901522</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31237196882344214423913275000380</t>
+          <t>44745448015810043974420105042705</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5939754217660512135252830984902</t>
+          <t>9619404035251431690410156141253</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38111811200407141665021932625217</t>
+          <t>08725802375409634472788214987203</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2040379048511895522480332590644</t>
+          <t>3252040212235323007714494217813</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>01065682251121521828184481719083</t>
+          <t>93694368219017064305464344024845</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1598033445221397556355769687809</t>
+          <t>0474213046054443322006905365005</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>912443304152062262252460930322746721</t>
+          <t>346329313589642441944042219712936003</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4313215820063166235031323951123</t>
+          <t>2647326325404655672543479516522</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24102710366956000605163480186750</t>
+          <t>67049460639365356248601147286803</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3305755210125150422810741431036</t>
+          <t>2187593343705970114012701251333</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62476031219461158045213012281218</t>
+          <t>38000149791450539098014341333183</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5445711424294932176136733554776</t>
+          <t>0141692621961448233242706495096</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9240778415812458050188884037</t>
+          <t>1504185059852569342896200643</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>312941411245872953796593493250674390193400501</t>
+          <t>685053310452250406457172650726022854221172534</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1803064788289424530477291500048014441515</t>
+          <t>9510685310305361247046639411227161936039</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>396810206216919229203837532743738167941876150</t>
+          <t>831098045961491247032619140535458446332816003</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2044399071165845593465153154155104454643</t>
+          <t>4023217011324506850845072711303382241857</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4752502191462221822405186402</t>
+          <t>0418820657106045038056276461</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>37751403623725584711762</t>
+          <t>90670144147453588523149</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>435711415070300134331509141716274533361</t>
+          <t>535223430106692549287795090457032246431</t>
         </is>
       </c>
       <c r="J30" s="2" t="n"/>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34261426135212336277645280452630</t>
+          <t>13240163032633324820415143510086</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3216224763044435468176121149184</t>
+          <t>0330736200511548774582201134610</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82453612427763888992113336112255</t>
+          <t>53929459398311525038692610051120</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>04560822513639769042346505538023</t>
+          <t>41329135152035050954064226145758</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>107332585719034375445525195692080819410852352</t>
+          <t>240244252016916319880021461982521117491460092</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0213154546042630315113654422470445145039</t>
+          <t>2162848659519200425915071015002832230320</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74321759143522175476912575049510</t>
+          <t>65056908957356357812009641507862</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>3242172360173428493401489021141</t>
+          <t>3158848821231936923543334790572</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47351875730366532103181594084521</t>
+          <t>22381973023052213332571468054915</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17503157203142259552062595332050</t>
+          <t>51140101563590310312198355485800</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7172027195133070005548401075025</t>
+          <t>5540644274811225561461529100691</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>5246445651809564983327811740508</t>
+          <t>9545111812243579153220560314548</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2911231010900720214295314175245</t>
+          <t>3355240935302380510669278103255</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>413864047524310275505710503531315900054382583</t>
+          <t>503509214402935532155631587412405206019352225</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>4605212141853554555007056108913001354128</t>
+          <t>5204334131871041356577493432491954457119</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>526573292730451782359508520070702292039231215</t>
+          <t>129141429564067512474744473323315030478300901</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0512140008146515553355599180140552542318</t>
+          <t>6058603585644863513961125436585071123422</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0821819261532312800006335619</t>
+          <t>0180838215180268126062654358</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>03763519050340733532511551823114</t>
+          <t>82473421211948855773027215521684</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31232753522625227331973772121141</t>
+          <t>06041732118092103034150362638414</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>36141502399248209113304303304761</t>
+          <t>01430010159041583224660349620241</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>商户单号25147121721424948443010314781</t>
+          <t>商户单号32294501444720259264522560860</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5722416569528335436164848862</t>
+          <t>6728241410430111770047238035</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>25147121721424948443010314781</t>
+          <t>32294501444720259264522560860</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>商户单号37782594723091225422622009343</t>
+          <t>商户单号01552810531559442418897047532</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6358703406013200611078709487</t>
+          <t>0604014382773822962442236652</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>37782594723091225422622009343</t>
+          <t>01552810531559442418897047532</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>675666570403027541304350043130096821242931724</t>
+          <t>312698395115362037484966585337661635186391091</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>1852618295176733187926414808223081598155</t>
+          <t>5225348216391074021510030846060352900237</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8822721395004447704265144230</t>
+          <t>1993152815011700310373417210</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>kj137230286415134080158605</t>
+          <t>kj911256710240360404448550</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1052135146400251200031371604</t>
+          <t>5907150950227549444076812138</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>product_SZ_90326650078100944</t>
+          <t>product_SZ_34111305610325100</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8850428545175691532295307150</t>
+          <t>0803333519110200916516235194</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ZY0368344034223117342572</t>
+          <t>ZY4042531423449604160238</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>81132831251163212115714183114754</t>
+          <t>19993415726422139304102522733127</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>13502352252227443857385844352089</t>
+          <t>50311777530022210339725211219307</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3351521152421821053703481190</t>
+          <t>1046257593129021276527149478</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>760552169608529185456030094721</t>
+          <t>298533232283732674572521973849</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2584450104203144926505152200</t>
+          <t>6826011473434843507226002290</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>9430052435535848743</t>
+          <t>5802416600910957424</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>056301144411725133557113046209499377399850246</t>
+          <t>584195040460001305052343434140241573637442701</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>4641316453720433258652003220355712</t>
+          <t>7043432754310200412302233110601881</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>445516813460141227090722052213743453165540903</t>
+          <t>754045711232056395122230156148484225332755039</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>5930212214557406562013184442960208</t>
+          <t>0366364801582029145225590580355622</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6703516536882574118232335832</t>
+          <t>9541533018138982106305544545</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>product_SZ_42153521729934754</t>
+          <t>product_SZ_10413611251151440</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3514959204210436680242125829</t>
+          <t>5321210053433010005521531323</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>product_SH_81253523982850415</t>
+          <t>product_SH_75113485288402471</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>9611214281200123385815731600</t>
+          <t>5098414228007292829655321042</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>30742621334485855544202534064244</t>
+          <t>34113955155422299306725053415133</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>4562401555671103084835311703</t>
+          <t>9724542197565045012464983215</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>kj202521090547522357132217</t>
+          <t>kj411033520122414322420218</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1536350853152409944403044073</t>
+          <t>4044254885781619237220250010</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>product_SH_768218420115108326</t>
+          <t>product_SH_349411251054922254</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3390401835231340318457335495</t>
+          <t>1389562730365931286024352333</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>553226455937761590007247338350</t>
+          <t>077355240720011942208416509101</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1035211141726428282611110537</t>
+          <t>0288646122224300429434504980</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>团购-美团微信小程序-35598412006195274354454374922834</t>
+          <t>团购-美团微信小程序-21555066967721922299381287341047</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1753437560952021353914462471</t>
+          <t>6831283424415448429473770985</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>20261005124129U78544375420654135</t>
+          <t>20261005124129U90473659111043320</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3655303514052933252834017187</t>
+          <t>9041222145559572807278004154</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>12941802400763103341290395608351</t>
+          <t>00164566131105551840618139905735</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>94066012422105383060076035376019</t>
+          <t>41561274403224328701337524112062</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>8528059642599033332305610403</t>
+          <t>5893240002351715875881499321</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1179357516749548152242249332</t>
+          <t>1402686543023682216553356509</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3501155069362262321053314922</t>
+          <t>9765835543340800349204644051</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>13633841225559438476</t>
+          <t>54557483143360005236</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>02220352146402962503115571072520</t>
+          <t>04903180481503816655304854439550</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>01013454442431592002651437157547</t>
+          <t>10748038244603629229151263010157</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3200771324373543310254482217</t>
+          <t>0795405378886323881414220545</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>5823572063001894547413308624</t>
+          <t>9321544041252059313900287554</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>团购-美团微信小程序-21245193900035224050111034149706</t>
+          <t>团购-美团微信小程序-20811118348241148617348888253324</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>6241493022221013146633413927</t>
+          <t>2114352556529314410488202088</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>20261002202345U10023332351102443</t>
+          <t>20261002202345U46343030477694231</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>0950904733027003322541723618</t>
+          <t>9114646024342448449471101210</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>55320523494090728354639284045065</t>
+          <t>16353449521851501170953135901059</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>14851054623311291095750926044047</t>
+          <t>05331021000007204081529581475530</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>4057621540446636757455501814</t>
+          <t>1293780003534435402503550572</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>250657595422305244621419231687</t>
+          <t>053092810117268377404661128257</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>3715151724190404259504965040</t>
+          <t>5200626332305424655245030187</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>5503057292954751075589483138</t>
+          <t>0098627301380342135084232975</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>3231228310221816294400458163</t>
+          <t>2309281440273435838215031290</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>509045178057555291834781254552</t>
+          <t>139435013301923545221083231452</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>团购-大众点评微信小程序-32324218549575792247461087155736</t>
+          <t>团购-大众点评微信小程序-95256770260560445975081404044297</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>5654236203531525961633218074</t>
+          <t>5421095267026406598878422047</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>20261001131314U94641549732202850</t>
+          <t>20261001131314U40394303008505736</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>团购-大众点评微信小程序-29140156611825754100815575610251</t>
+          <t>团购-大众点评微信小程序-95939047427137361853056753520859</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2860953107446189481140732389</t>
+          <t>3305449464200317015523544236</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>20261001131210U71674059566816751</t>
+          <t>20261001131210U79801666147426710</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>KFC_PRE_PLUSWX30718248205112470376432</t>
+          <t>KFC_PRE_PLUSWX21616050054641143667442</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>1158504334967195250329605721</t>
+          <t>1334233001550431345554280241</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>WX30718248205112470376432</t>
+          <t>WX21616050054641143667442</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>1050156215144154860331820252</t>
+          <t>2753994689145554047213201152</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>3451740105537235234443380374</t>
+          <t>3476169568830340175002849493</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>product_SZ_82638263062103354</t>
+          <t>product_SZ_54680854103345515</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>11071600379003023471000905430539</t>
+          <t>00272253727325407050456921593520</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>62564144835731960901472544225500</t>
+          <t>33235844212226383508777904235327</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4859413090434644039436404431</t>
+          <t>7282433542707379283123340188</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>255354230270318650323125371871</t>
+          <t>454215223135531233283099351831</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>268230971423427428402855671302424510580</t>
+          <t>718823320140544337343433623015052100517</t>
         </is>
       </c>
       <c r="J83" s="2" t="n"/>
